--- a/school_application_forms/019_school_admission_form--school_application_forms.xlsx
+++ b/school_application_forms/019_school_admission_form--school_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1309,8 +1309,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'class_1'}</t>
+          <t>class_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Class 1'}</t>
+          <t>Class 1</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'class_2'}</t>
+          <t>class_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Class 2'}</t>
+          <t>Class 2</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_6,_'label':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 6, 'label': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'male',_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'male', 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'female',_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'female', 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'grade_1'}</t>
+          <t>grade_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Grade 1'}</t>
+          <t>Grade 1</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'grade_2'}</t>
+          <t>grade_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Grade 2'}</t>
+          <t>Grade 2</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'grade_3'}</t>
+          <t>grade_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Grade 3'}</t>
+          <t>Grade 3</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'english',_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'English', 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'spanish',_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish', 'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'french',_'label':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'French', 'label': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1542,12 +1542,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'american',_'label':_'american'}</t>
+          <t>american</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'American', 'label': 'American'}</t>
+          <t>American</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'chinese',_'label':_'chinese'}</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Chinese', 'label': 'Chinese'}</t>
+          <t>Chinese</t>
         </is>
       </c>
     </row>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'indian',_'label':_'indian'}</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Indian', 'label': 'Indian'}</t>
+          <t>Indian</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'feet',_'label':_'feet'}</t>
+          <t>feet</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'feet', 'label': 'feet'}</t>
+          <t>feet</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'inches',_'label':_'inches'}</t>
+          <t>inches</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'inches', 'label': 'inches'}</t>
+          <t>inches</t>
         </is>
       </c>
     </row>
